--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -637,31 +637,27 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +689,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -761,19 +757,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -817,7 +813,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -837,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -850,24 +846,24 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -880,19 +876,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -902,12 +898,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +932,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -969,7 +965,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -979,7 +975,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -999,34 +995,34 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1040,47 +1036,1467 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>06:50</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>1/4</t>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 22分钟</t>
+          <t>SHMAAS末次终点ETA推算：07:30采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -995,26 +995,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1051,7 +1047,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1071,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1110,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+          <t>08:00采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1141,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1228,29 +1224,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1260,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,12 +1280,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1299,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1352,19 +1348,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1379,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1471,19 +1467,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1498,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1547,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1590,19 +1586,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1617,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1646,7 +1642,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1666,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1709,24 +1705,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金杨路枣庄路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±8分钟</t>
+          <t>08:00采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1736,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1828,19 +1824,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>08:00采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1855,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1904,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1947,19 +1943,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1974,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2003,7 +1999,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2023,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2066,24 +2062,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+          <t>08:00采样：该车到重点站巨峰路成园路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2093,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2122,7 +2118,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2142,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2254,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2296,19 +2292,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>08:00采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2323,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2352,7 +2348,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2372,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2385,24 +2381,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2415,7 +2411,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2427,7 +2423,7 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+          <t>08:00采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2437,12 +2433,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2456,47 +2452,745 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>85.5</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>9/15</t>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -752,31 +752,27 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -784,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -808,12 +804,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -838,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -888,12 +884,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -903,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1110,26 +1106,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:18采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1137,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1166,7 +1158,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1176,22 +1168,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1229,24 +1221,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1348,24 +1340,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站云山路灵山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1375,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1467,26 +1459,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:18采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1494,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1523,7 +1511,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1533,22 +1521,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1586,24 +1574,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站云山路灵山路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1613,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1650,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1705,24 +1693,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站巨峰路成园路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
+          <t>08:18采样：该车到重点站杨高北路（外高桥保税区南站） ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1732,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1769,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1829,14 +1817,14 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站张杨北路博兴路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1851,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,7 +1888,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1943,19 +1931,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金高路俱进路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站五莲路归昌路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1970,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2007,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2062,24 +2050,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站巨峰路成园路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±6分钟</t>
+          <t>08:18采样：该车到重点站杨高北路（外高桥保税区南站） ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2292,19 +2280,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>08:18采样：该车到重点站五莲路凌河路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2319,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2356,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2480,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2530,19 +2518,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±5分钟</t>
+          <t>08:18采样：该车到重点站金高路行泰路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2557,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2586,7 +2574,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2606,12 +2594,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,7 +2728,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2765,14 +2753,14 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±5分钟</t>
+          <t>08:18采样：该车到重点站云山路灵山路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2787,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2801,7 +2789,7 @@
       <c r="T20" s="2" t="inlineStr"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2816,7 +2804,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2841,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2956,7 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2978,7 +2966,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2998,30 +2986,34 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3035,7 +3027,7 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3045,33 +3037,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3185,12 +3181,361 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站云山路灵山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1471,10 +1471,14 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:18采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,12 +1510,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1531,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1569,29 +1573,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站云山路灵山路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数13分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,12 +1629,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1640,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1688,29 +1692,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站杨高北路（外高桥保税区南站） ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,12 +1748,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1759,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1811,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1824,7 +1828,7 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站张杨北路博兴路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,12 +1867,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1878,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1926,29 +1930,29 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站五莲路归昌路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,12 +1986,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -1997,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2045,29 +2049,29 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站杨高北路（外高桥保税区南站） ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2101,12 +2105,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2116,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2169,19 +2173,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:00采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2216,17 +2220,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2236,13 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2283,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2292,7 +2300,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站五莲路凌河路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2307,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2331,12 +2339,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2346,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2394,24 +2402,24 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2426,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2450,12 +2458,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2475,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2513,29 +2521,29 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站金高路行泰路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2545,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,12 +2577,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2594,12 +2602,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2637,19 +2645,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
@@ -2660,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2684,17 +2692,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2704,13 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2748,26 +2760,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:18采样：该车到重点站云山路灵山路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2775,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2804,7 +2812,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2814,17 +2822,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2867,19 +2875,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+          <t>09:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2894,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2923,7 +2931,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2943,7 +2951,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -2986,24 +2994,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±8分钟</t>
+          <t>同车下一次反向发车10:20，减去该车自身同类时段历史终点停站中位数22分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3013,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3042,7 +3050,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3052,22 +3060,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3110,14 +3118,14 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3132,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3161,7 +3169,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3181,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3335,19 +3343,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3362,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3391,7 +3399,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3411,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3454,24 +3462,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±6分钟</t>
+          <t>09:20采样：该车到重点站巨峰路成园路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3481,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3510,32 +3518,1103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站杨高北路夏碧路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>09:20采样：该车到重点站金高路俱进路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2760,19 +2760,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:20采样，终点ETA 19分钟</t>
+          <t>SHMAAS末次终点ETA推算：09:40采样，终点ETA 1分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2875,24 +2875,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±6分钟</t>
+          <t>同车下一次反向发车10:10，减去该车自身同类时段历史终点停站中位数2分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2989,29 +2989,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车10:20，减去该车自身同类时段历史终点停站中位数22分钟，约±10分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3118,14 +3118,14 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3338,29 +3338,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站五莲路荷泽路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3409,22 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3457,29 +3457,29 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站巨峰路成园路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3576,29 +3576,29 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站杨高北路夏碧路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3647,22 +3647,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3695,29 +3695,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金杨路枣庄路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3814,29 +3814,29 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>09:20采样：该车到重点站金高路俱进路 ETA 30分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3950,14 +3950,10 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3965,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3994,7 +3990,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4019,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4057,19 +4053,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站五莲路归昌路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4084,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4113,7 +4109,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4133,12 +4129,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4176,19 +4172,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车11:10，减去该车自身同类时段历史终点停站中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4203,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4232,7 +4228,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4242,22 +4238,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4295,19 +4291,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -4322,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4351,7 +4347,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4371,12 +4367,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4414,24 +4410,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±12分钟</t>
+          <t>10:20采样：该车到重点站杨高北路航津路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4441,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4465,12 +4461,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4490,12 +4486,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4503,24 +4499,24 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4533,34 +4529,34 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+          <t>10:20采样：该车到重点站张杨北路金桥路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4574,47 +4570,761 @@
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站云山路灵山路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站和龙路花山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
-        <is>
-          <t>9/18</t>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,22 +3060,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,22 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3700,24 +3700,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3950,10 +3950,14 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3961,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,12 +3989,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4015,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4048,29 +4052,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站五莲路归昌路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4080,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,12 +4108,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4119,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4184,14 +4188,10 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车11:10，减去该车自身同类时段历史终点停站中位数22分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:40采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4286,29 +4286,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4405,29 +4405,29 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站杨高北路航津路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4524,29 +4524,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站张杨北路金桥路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4595,22 +4595,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4648,24 +4648,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站云山路灵山路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±6分钟</t>
+          <t>10:50采样：该车到重点站五莲路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4762,29 +4762,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站和龙路花山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4833,22 +4833,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4881,29 +4881,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4952,22 +4952,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5005,24 +5005,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+          <t>11:20采样：该车到重点站巨峰路成园路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5124,19 +5124,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+          <t>11:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5213,24 +5213,24 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5243,34 +5243,34 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5284,47 +5284,880 @@
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X41" s="2" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>84.7</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4767,12 +4767,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5000,29 +5000,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站巨峰路成园路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5071,22 +5071,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5309,22 +5309,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5357,24 +5357,24 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5428,22 +5428,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5476,29 +5476,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5547,22 +5547,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5595,29 +5595,29 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5719,26 +5719,22 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5746,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5770,17 +5766,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5790,17 +5786,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5838,19 +5834,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+          <t>12:20采样：该车到重点站金高路东靖路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5865,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5894,7 +5890,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5914,12 +5910,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5957,24 +5953,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±6分钟</t>
+          <t>12:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5984,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6013,7 +6009,7 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6033,7 +6029,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6103,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6152,12 +6148,607 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,22 +2822,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,22 +4476,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5481,24 +5481,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5600,12 +5600,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5714,27 +5714,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5742,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,37 +5770,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5829,29 +5833,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站金高路东靖路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5861,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5885,12 +5889,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5910,12 +5914,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5953,24 +5957,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>12:40采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5980,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6029,12 +6033,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6072,24 +6076,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±6分钟</t>
+          <t>12:40采样：该车到重点站杨高北路夏碧路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6099,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6128,7 +6132,7 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6148,12 +6152,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6191,24 +6195,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+          <t>12:40采样：该车到重点站金杨路枣庄路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6218,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6247,7 +6251,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6267,12 +6271,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6456,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6575,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6624,12 +6628,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6743,12 +6747,131 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,22 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4595,22 +4595,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4833,17 +4833,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,22 +4952,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5719,24 +5719,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5838,24 +5838,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,22 +5904,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5952,29 +5952,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6023,17 +6023,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6076,26 +6076,22 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站杨高北路夏碧路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6103,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6127,12 +6123,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6142,22 +6138,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6190,29 +6186,29 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:40采样：该车到重点站金杨路枣庄路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6222,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,12 +6242,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6271,12 +6267,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6314,26 +6310,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 51分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6341,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6365,17 +6357,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6385,12 +6377,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6433,19 +6425,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>13:20采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6460,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6489,7 +6481,7 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6509,7 +6501,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6552,24 +6544,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±5分钟</t>
+          <t>13:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6579,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6608,7 +6600,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6628,12 +6620,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6817,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6866,12 +6858,488 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>90.4</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,14 +2235,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,17 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,22 +5071,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,17 +5314,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,22 +5428,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5547,17 +5547,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5790,17 +5790,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5957,24 +5957,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6071,27 +6071,31 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 28分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6099,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,12 +6127,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6148,7 +6152,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6203,12 +6207,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6218,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6257,22 +6261,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6305,27 +6309,31 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 51分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6333,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6357,17 +6365,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6377,17 +6385,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6420,24 +6428,24 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站金杨路枣庄路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6452,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,12 +6484,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6491,22 +6499,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6547,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6556,12 +6564,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站杨高北路夏碧路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6571,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,12 +6603,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6610,17 +6618,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6658,29 +6666,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6690,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6714,12 +6722,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6739,12 +6747,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6782,26 +6790,22 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6809,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6833,17 +6837,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6853,17 +6857,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6901,26 +6905,22 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 61分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6952,17 +6952,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7020,24 +7020,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+          <t>14:20采样：该车到重点站金高路东靖路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -7270,12 +7270,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±13分钟</t>
+          <t>14:20采样：该车到重点站丁香路民生路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7309,37 +7309,509 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>4/18</t>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1168,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,14 +2707,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,22 +2822,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2875,19 +2875,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车10:10，减去该车自身同类时段历史终点停站中位数2分钟，约±5分钟</t>
+          <t>09:40采样：该车到重点站丁香路民生路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数4分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,22 +3528,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,22 +4476,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4595,22 +4595,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4638,36 +4638,32 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程32%处后消失；随后反向物理轨迹由seq21推进至seq29，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:50采样：该车到重点站五莲路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4675,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4683,10 +4679,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>张杨北路博兴路</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq14映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4699,37 +4707,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4843,12 +4851,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4962,12 +4970,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5081,12 +5089,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5114,36 +5122,32 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程42%处后消失；随后反向物理轨迹由seq22推进至seq27，推进5站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -5151,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5159,10 +5163,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq18映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5175,32 +5191,32 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5270,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5324,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5438,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5557,12 +5573,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,17 +5682,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5746,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,22 +5801,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,22 +5920,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5984,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6033,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6152,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6271,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6395,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6509,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6628,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,17 +6753,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6785,12 +6801,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -6802,10 +6818,14 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6813,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6837,37 +6857,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6900,27 +6920,31 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 61分钟</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6928,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6952,37 +6976,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7015,29 +7039,29 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站金高路东靖路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7047,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7071,12 +7095,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7096,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7139,26 +7163,22 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7166,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7195,7 +7215,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7215,12 +7235,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7253,29 +7273,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站丁香路民生路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7285,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7309,12 +7329,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7334,12 +7354,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7377,24 +7397,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+          <t>15:20采样：该车到重点站巨峰路成园路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7404,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7433,7 +7453,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7453,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7496,19 +7516,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 52分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
@@ -7519,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7548,7 +7568,7 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7573,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7611,24 +7631,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±10分钟</t>
+          <t>15:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7638,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7667,7 +7687,7 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7687,12 +7707,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7730,19 +7750,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7757,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7786,32 +7806,980 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站金高路俱进路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>86.2</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,22 +3060,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,22 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,17 +4238,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4841,22 +4841,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,22 +4960,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,17 +5079,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程42%处后消失；随后反向物理轨迹由seq22推进至seq27，推进5站，达到≥2站确认条件</t>
+          <t>原方向在全程42%处后消失；随后反向物理轨迹由seq22推进至seq36，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,17 +5444,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,17 +6277,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,17 +6515,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,17 +6634,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,22 +7110,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7158,27 +7158,31 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7186,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,12 +7214,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7225,17 +7229,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7278,12 +7282,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7305,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,22 +7348,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7396,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -7402,14 +7406,14 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站巨峰路成园路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7424,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,12 +7452,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7463,17 +7467,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7511,27 +7515,31 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 52分钟</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7539,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7563,37 +7571,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7631,26 +7639,22 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:00采样，终点ETA 10分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7658,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7687,7 +7691,7 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7697,17 +7701,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7745,29 +7749,29 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7777,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,12 +7805,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7816,17 +7820,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7869,26 +7873,22 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金高路俱进路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7988,19 +7988,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8035,37 +8035,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8103,26 +8103,22 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8130,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8159,7 +8155,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8179,12 +8175,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8222,24 +8218,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>16:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8249,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8278,7 +8274,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8298,12 +8294,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8341,24 +8337,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+          <t>16:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8368,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8397,7 +8393,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8417,12 +8413,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8460,19 +8456,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+          <t>16:20采样：该车到重点站五莲路凌河路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8487,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8516,7 +8512,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8536,12 +8532,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8579,24 +8575,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+          <t>16:20采样：该车到重点站杨高北路航津路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8606,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8635,7 +8631,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8655,12 +8651,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8698,24 +8694,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±6分钟</t>
+          <t>16:20采样：该车到重点站张杨北路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8725,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8754,32 +8750,976 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站云山路灵山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站杨高北路航津路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z70" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>87.3</t>
         </is>
       </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2875,19 +2875,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:40采样：该车到重点站丁香路民生路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数4分钟，约±5分钟</t>
+          <t>09:40采样：该车到重点站丁香路民生路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数3分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,17 +3528,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4595,22 +4595,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,22 +5325,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,17 +5801,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,22 +5920,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,22 +6396,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,17 +6753,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,17 +6872,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6991,22 +6991,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7868,27 +7868,31 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7896,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,12 +7924,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7935,17 +7939,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8011,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8065,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8098,27 +8102,31 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 30分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8126,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8150,12 +8158,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8165,17 +8173,17 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8213,29 +8221,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8245,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8269,12 +8277,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8284,22 +8292,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8332,29 +8340,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8364,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8388,12 +8396,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8403,17 +8411,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8451,29 +8459,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路凌河路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8483,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8507,12 +8515,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8522,17 +8530,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8570,7 +8578,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8587,12 +8595,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站杨高北路航津路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8602,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,12 +8634,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8641,22 +8649,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8689,29 +8697,29 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站张杨北路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8721,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8745,12 +8753,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8770,12 +8778,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8813,26 +8821,22 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站云山路灵山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8840,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,12 +8868,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8889,12 +8893,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8932,19 +8936,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站杨高北路航津路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±7分钟</t>
+          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8959,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9008,12 +9012,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9051,24 +9055,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9078,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9107,7 +9111,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9127,7 +9131,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9193,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9285,19 +9289,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9312,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9341,7 +9345,7 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9361,12 +9365,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9404,19 +9408,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9431,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9460,7 +9464,7 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9480,12 +9484,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9523,19 +9527,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站金杨路枣庄路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9550,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9579,7 +9583,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9599,12 +9603,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9626,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -9665,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9679,7 +9683,7 @@
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -9719,7 +9723,840 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,22 +3647,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,17 +4960,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7348,17 +7348,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8583,24 +8583,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8768,22 +8768,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8816,12 +8816,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -8833,10 +8833,14 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8844,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,12 +8872,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8936,26 +8940,22 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:30采样，终点ETA 24分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9002,17 +9002,17 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9050,29 +9050,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9289,24 +9289,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±6分钟</t>
+          <t>17:40采样：该车到重点站金高路行泰路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9408,19 +9408,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>17:40采样：该车到重点站五莲路归昌路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9484,12 +9484,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9527,19 +9527,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金杨路枣庄路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>17:40采样：该车到重点站五莲路凌河路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9761,24 +9761,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±6分钟</t>
+          <t>17:40采样：该车到重点站五莲路凌河路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9880,24 +9880,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±10分钟</t>
+          <t>17:40采样：该车到重点站云山路灵山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9999,24 +9999,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±8分钟</t>
+          <t>17:40采样：该车到重点站杨高北路航津路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10118,19 +10118,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+          <t>17:40采样：该车到重点站张杨北路金桥路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10194,12 +10194,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10551,12 +10551,250 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,17 +4238,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,22 +5325,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,17 +5444,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,12 +6039,12 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,22 +6396,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,17 +6515,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,22 +7586,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7701,17 +7701,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,22 +8054,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8940,19 +8940,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:30采样，终点ETA 24分钟</t>
+          <t>SHMAAS末次终点ETA推算：17:50采样，终点ETA 18分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9055,24 +9055,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9169,27 +9169,31 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9197,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9221,37 +9225,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9284,24 +9288,24 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站金高路行泰路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9316,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9340,12 +9344,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9365,7 +9369,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9408,26 +9412,22 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站五莲路归昌路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9484,12 +9484,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9522,29 +9522,29 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站五莲路凌河路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9646,19 +9646,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 30分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9693,37 +9693,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站五莲路凌河路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
+          <t>18:20采样：该车到重点站花山路杨高北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数11分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9880,19 +9880,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站云山路灵山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
+          <t>18:20采样：该车到重点站金高路行泰路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9999,24 +9999,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站杨高北路航津路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±7分钟</t>
+          <t>同车下一次反向发车19:25，减去该车自身同类时段历史终点停站中位数12分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10065,22 +10065,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:40采样：该车到重点站张杨北路金桥路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>18:20采样：该车到重点站金高路行泰路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10237,19 +10237,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±5分钟</t>
+          <t>18:20采样：该车到重点站金高路东靖路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10356,24 +10356,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+          <t>18:20采样：该车到重点站杨高北路航津路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10475,24 +10475,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±9分钟</t>
+          <t>18:20采样：该车到重点站张杨北路金桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -10606,12 +10606,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±7分钟</t>
+          <t>18:20采样：该车到重点站花山路大同路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10718,19 +10718,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±13分钟</t>
+          <t>18:20采样：该车到重点站云山路灵山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,37 +10764,743 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X87" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y87" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z87" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>94.2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
+      <c r="AA92" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1168,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,22 +3528,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3647,22 +3647,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7939,22 +7939,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8173,17 +8173,17 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8292,22 +8292,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8768,22 +8768,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9646,19 +9646,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 30分钟</t>
+          <t>SHMAAS末次终点ETA推算：18:30采样，终点ETA 16分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
@@ -9718,12 +9718,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9756,29 +9756,29 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站花山路杨高北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数11分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9812,12 +9812,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9827,22 +9827,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9875,29 +9875,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金高路行泰路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9946,17 +9946,17 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9994,29 +9994,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车19:25，减去该车自身同类时段历史终点停站中位数12分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10113,29 +10113,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金高路行泰路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10194,12 +10194,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10232,24 +10232,24 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金高路东靖路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10303,22 +10303,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10351,29 +10351,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站杨高北路航津路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10470,29 +10470,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站张杨北路金桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10526,12 +10526,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10594,26 +10594,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站花山路大同路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10621,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10645,12 +10641,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10660,22 +10656,22 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10713,26 +10709,22 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站云山路灵山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10740,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10769,7 +10761,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10789,12 +10781,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10832,24 +10824,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±8分钟</t>
+          <t>19:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10859,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10888,7 +10880,7 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10908,12 +10900,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11066,19 +11058,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+          <t>19:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11093,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11122,7 +11114,7 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11142,7 +11134,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11208,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11257,12 +11249,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11300,24 +11292,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11327,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11356,7 +11348,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11376,12 +11368,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11495,12 +11487,488 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
           <t>84.8</t>
         </is>
       </c>
-      <c r="AC93" s="2" t="inlineStr">
+      <c r="AC94" s="2" t="inlineStr">
         <is>
           <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,17 +3528,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4727,17 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7939,17 +7939,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9827,17 +9827,17 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9946,22 +9946,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,17 +10308,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10589,27 +10589,31 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10617,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,12 +10645,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10666,12 +10670,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10704,27 +10708,31 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 20分钟</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10732,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10756,12 +10764,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10781,12 +10789,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10819,29 +10827,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金杨路金口路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10851,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10875,12 +10883,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10900,12 +10908,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10938,27 +10946,31 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -10966,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10990,17 +11002,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11010,12 +11022,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11053,29 +11065,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±12分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11085,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,12 +11121,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11124,17 +11136,17 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11172,27 +11184,31 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11200,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,17 +11240,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11244,17 +11260,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11287,24 +11303,24 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11319,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11343,12 +11359,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11368,12 +11384,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11406,29 +11422,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11438,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11462,12 +11478,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11487,7 +11503,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11525,29 +11541,29 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11557,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11581,12 +11597,12 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11596,17 +11612,17 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11649,26 +11665,22 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 58分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11676,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11700,17 +11712,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11720,17 +11732,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11768,24 +11780,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±11分钟</t>
+          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数25分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11795,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11824,7 +11836,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11834,22 +11846,22 @@
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11887,24 +11899,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±6分钟</t>
+          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11914,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11943,32 +11955,389 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y97" s="2" t="inlineStr">
+      <c r="Y98" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z97" s="2" t="inlineStr">
+      <c r="Z98" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA97" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
-        <is>
-          <t>9/18</t>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,17 +3528,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4727,17 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7939,17 +7939,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9827,17 +9827,17 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9951,17 +9951,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10065,17 +10065,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,17 +10308,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11427,24 +11427,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11493,17 +11493,17 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11665,19 +11665,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 58分钟</t>
+          <t>SHMAAS末次终点ETA推算：20:50采样，终点ETA 18分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11712,17 +11712,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11732,17 +11732,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11780,26 +11780,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车21:40，减去该车自身同类时段历史终点停站中位数25分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:00采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11807,7 +11803,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11831,17 +11827,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11851,17 +11847,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11894,24 +11890,24 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11926,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11950,12 +11946,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11975,12 +11971,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12013,29 +12009,29 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12045,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12069,12 +12065,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12094,7 +12090,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12117,7 +12113,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -12137,7 +12133,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>22:29</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -12164,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12178,7 +12174,7 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="V99" s="2" t="inlineStr">
@@ -12203,17 +12199,17 @@
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12226,7 +12222,7 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -12256,34 +12252,34 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12307,37 +12303,275 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-20-浦东78路.xlsx
+++ b/data/export/2026-09-20-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12014,24 +12014,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12090,12 +12090,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12145,12 +12145,12 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+          <t>21:50采样：该车到重点站金高路东靖路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12247,29 +12247,29 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>50分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
@@ -12328,12 +12328,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12371,24 +12371,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±8分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
